--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.7556908862368</v>
+        <v>6.29779976901348</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55108684727762</v>
+        <v>6.102051612682613</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F2" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.65302114488743</v>
+        <v>5.793615936044208</v>
       </c>
       <c r="D3" t="n">
-        <v>35.54892897789183</v>
+        <v>5.776700958907423</v>
       </c>
       <c r="E3" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F3" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.407204880883389</v>
+        <v>1.528670793143551</v>
       </c>
       <c r="D4" t="n">
-        <v>9.790059836347785</v>
+        <v>1.590884723406515</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F4" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.78392974589254</v>
+        <v>4.514888583707537</v>
       </c>
       <c r="D5" t="n">
-        <v>27.25074793483952</v>
+        <v>4.428246539411423</v>
       </c>
       <c r="E5" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F5" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.49254471099221</v>
+        <v>9.180038515536234</v>
       </c>
       <c r="D6" t="n">
-        <v>56.38998918300531</v>
+        <v>9.163373242238363</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F6" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.27268334851259</v>
+        <v>8.981811044133295</v>
       </c>
       <c r="D7" t="n">
-        <v>54.64230387425942</v>
+        <v>8.879374379567157</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F7" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.47696644318177</v>
+        <v>4.465007047017038</v>
       </c>
       <c r="D8" t="n">
-        <v>27.01768238696219</v>
+        <v>4.390373387881355</v>
       </c>
       <c r="E8" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F8" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.44194833747294</v>
+        <v>9.496816604839355</v>
       </c>
       <c r="D9" t="n">
-        <v>58.73502920205789</v>
+        <v>9.544442245334409</v>
       </c>
       <c r="E9" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F9" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.07926183845786</v>
+        <v>4.725380048749402</v>
       </c>
       <c r="D10" t="n">
-        <v>28.9775799833061</v>
+        <v>4.708856747287242</v>
       </c>
       <c r="E10" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F10" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.31739270406833</v>
+        <v>5.414076314411104</v>
       </c>
       <c r="D11" t="n">
-        <v>32.71833531636176</v>
+        <v>5.316729488908786</v>
       </c>
       <c r="E11" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F11" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.11223868198368</v>
+        <v>7.330738785822348</v>
       </c>
       <c r="D12" t="n">
-        <v>44.49444662855029</v>
+        <v>7.230347577139423</v>
       </c>
       <c r="E12" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F12" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.18756068353652</v>
+        <v>7.180478611074686</v>
       </c>
       <c r="D13" t="n">
-        <v>43.36452268812893</v>
+        <v>7.046734936820951</v>
       </c>
       <c r="E13" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F13" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>76.82877171500199</v>
+        <v>12.48467540368782</v>
       </c>
       <c r="D14" t="n">
-        <v>76.83291927843831</v>
+        <v>12.48534938274623</v>
       </c>
       <c r="E14" t="n">
-        <v>16.75005859757174</v>
+        <v>2.721884522105408</v>
       </c>
       <c r="F14" t="n">
-        <v>16.76220423019869</v>
+        <v>2.723858187407286</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
